--- a/Flow/202609/2026-09-25/AIDPC_アウトプットファイル設計/input/テスト用患者一覧_176件.xlsx
+++ b/Flow/202609/2026-09-25/AIDPC_アウトプットファイル設計/input/テスト用患者一覧_176件.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juny4\Desktop\appl\git\aipm_v0\Flow\202609\2026-09-25\AIDPC_アウトプットファイル設計\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D29C418-2219-4954-8BAB-7367CAA4E369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AF99A33-2D91-4288-9706-D70C0AE8E3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="1104" windowWidth="24984" windowHeight="14400" xr2:uid="{A35D368D-BE5E-44E5-AF62-74F39E2EDDF4}"/>
+    <workbookView xWindow="1056" yWindow="960" windowWidth="29112" windowHeight="14940" xr2:uid="{2DC5158F-559B-40CB-8CC8-56339E123BBD}"/>
   </bookViews>
   <sheets>
     <sheet name="患者一覧" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="112">
   <si>
     <t>患者番号</t>
   </si>
@@ -181,6 +181,9 @@
     <t>050050xx9900x0</t>
   </si>
   <si>
+    <t>050080xx99x0xx</t>
+  </si>
+  <si>
     <t>未算定</t>
   </si>
   <si>
@@ -196,142 +199,154 @@
     <t>060020xx97x0xx</t>
   </si>
   <si>
+    <t>060350xx99x0xx</t>
+  </si>
+  <si>
+    <t>050070xx99000x</t>
+  </si>
+  <si>
+    <t>110280xx97x00x</t>
+  </si>
+  <si>
+    <t>160780xx97xx0x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">060340XX03X00X </t>
+  </si>
+  <si>
+    <t>160760xx99xxxx</t>
+  </si>
+  <si>
+    <t>060130xx9700xx</t>
+  </si>
+  <si>
+    <t>999999xx99x9xx</t>
+  </si>
+  <si>
+    <t>060330xx01xxxx</t>
+  </si>
+  <si>
+    <t>161020xxxxx0xx</t>
+  </si>
+  <si>
+    <t>060185xx99x00x</t>
+  </si>
+  <si>
+    <t>080010xxxx0xxx</t>
+  </si>
+  <si>
+    <t>040040xx97x00x</t>
+  </si>
+  <si>
+    <t>070370xx97xxxx</t>
+  </si>
+  <si>
+    <t>060335xx0100xx</t>
+  </si>
+  <si>
+    <t>ケース</t>
+  </si>
+  <si>
+    <t>設定したDPC</t>
+  </si>
+  <si>
+    <t>設定した点数</t>
+  </si>
+  <si>
+    <t>AI 1番手のDPC</t>
+  </si>
+  <si>
+    <t>AI 1番手の点数</t>
+  </si>
+  <si>
+    <t>使った候補の自信度</t>
+  </si>
+  <si>
+    <t>期待: コード一致</t>
+  </si>
+  <si>
+    <t>期待: 評価</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>2番手以下のDPC・1番手より低い点数</t>
+  </si>
+  <si>
+    <t>010060xx97041x</t>
+  </si>
+  <si>
+    <t>6桁不一致</t>
+  </si>
+  <si>
+    <t>増収候補</t>
+  </si>
+  <si>
+    <t>1番手のDPC・点数と一致</t>
+  </si>
+  <si>
+    <t>完全一致</t>
+  </si>
+  <si>
+    <t>一致</t>
+  </si>
+  <si>
+    <t>2番手以下のDPC・1番手と同じ点数</t>
+  </si>
+  <si>
+    <t>実データに同点の候補がないため、点数は1番手の点数を設定</t>
+  </si>
+  <si>
+    <t>その他: AI側の点数が数値でない</t>
+  </si>
+  <si>
+    <t>AI点数が空のため点数一致は空</t>
+  </si>
+  <si>
+    <t>2番手以下のDPC・1番手より高い点数</t>
+  </si>
+  <si>
+    <t>アップコーディング候補</t>
+  </si>
+  <si>
+    <t>DPC・点数とも未設定</t>
+  </si>
+  <si>
+    <t>07040xxx97xxxx</t>
+  </si>
+  <si>
+    <t>要確認</t>
+  </si>
+  <si>
+    <t>040040xx02x0xx</t>
+  </si>
+  <si>
+    <t>その他: 先頭6桁だけ同じDPC・点数が文字列</t>
+  </si>
+  <si>
+    <t>7桁以降不一致</t>
+  </si>
+  <si>
+    <t>実データに該当候補がないため、1番手のDPCの7桁目以降を書き換えた仮のコード</t>
+  </si>
+  <si>
+    <t>060060xx9712xx</t>
+  </si>
+  <si>
+    <t>その他: 先頭6桁だけ同じDPC・点数は1番手と同じ</t>
+  </si>
+  <si>
     <t>060350xx97x0xx</t>
   </si>
   <si>
-    <t>050070xx99000x</t>
-  </si>
-  <si>
-    <t>110280xx97x00x</t>
-  </si>
-  <si>
-    <t>160780xx97xx0x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">060340XX03X00X </t>
-  </si>
-  <si>
-    <t>160760xx99xxxx</t>
-  </si>
-  <si>
-    <t>060130xx9700xx</t>
-  </si>
-  <si>
-    <t>999999xx99x9xx</t>
-  </si>
-  <si>
-    <t>060330xx01xxxx</t>
-  </si>
-  <si>
-    <t>161020xxxxx0xx</t>
-  </si>
-  <si>
-    <t>060185xx99x00x</t>
-  </si>
-  <si>
-    <t>080010xxxx0xxx</t>
-  </si>
-  <si>
-    <t>040040xx97x00x</t>
-  </si>
-  <si>
-    <t>070370xx97xxxx</t>
-  </si>
-  <si>
-    <t>060335xx0100xx</t>
-  </si>
-  <si>
-    <t>ケース</t>
-  </si>
-  <si>
-    <t>設定したDPC</t>
-  </si>
-  <si>
-    <t>設定した点数</t>
-  </si>
-  <si>
-    <t>AI 1番手のDPC</t>
-  </si>
-  <si>
-    <t>AI 1番手の点数</t>
-  </si>
-  <si>
-    <t>使った候補の自信度</t>
-  </si>
-  <si>
-    <t>期待: コード一致</t>
-  </si>
-  <si>
-    <t>期待: 点数一致</t>
-  </si>
-  <si>
-    <t>備考</t>
-  </si>
-  <si>
-    <t>2番手以下のDPC・1番手より低い点数</t>
-  </si>
-  <si>
-    <t>010060xx97041x</t>
-  </si>
-  <si>
-    <t>コード不一致</t>
-  </si>
-  <si>
-    <t>増収候補</t>
-  </si>
-  <si>
-    <t>1番手のDPC・点数と一致</t>
-  </si>
-  <si>
-    <t>コード一致</t>
-  </si>
-  <si>
-    <t>点数一致</t>
-  </si>
-  <si>
-    <t>2番手以下のDPC・1番手と同じ点数</t>
-  </si>
-  <si>
-    <t>実データに同点の候補がないため、点数は1番手の点数を設定</t>
-  </si>
-  <si>
-    <t>その他: AI側の点数が数値でない</t>
-  </si>
-  <si>
-    <t>AI点数が空のため点数一致は空</t>
-  </si>
-  <si>
-    <t>2番手以下のDPC・1番手より高い点数</t>
-  </si>
-  <si>
-    <t>アップコーディング</t>
-  </si>
-  <si>
-    <t>DPC・点数とも未設定</t>
-  </si>
-  <si>
-    <t>07040xxx97xxxx</t>
-  </si>
-  <si>
-    <t>040040xx02x0xx</t>
-  </si>
-  <si>
-    <t>その他: 点数が文字列</t>
-  </si>
-  <si>
-    <t>060060xx9712xx</t>
-  </si>
-  <si>
-    <t>その他: DPCのみ設定・点数空</t>
-  </si>
-  <si>
-    <t>その他: DPCの表記揺れ（大文字・末尾空白）</t>
-  </si>
-  <si>
-    <t>空白と大文字小文字は無視されてコード一致になるはず</t>
-  </si>
-  <si>
-    <t>その他: 候補にないDPC</t>
+    <t>その他: DPCの表記揺れ（大文字・末尾空白）・点数空</t>
+  </si>
+  <si>
+    <t>空白と大文字小文字は無視されて完全一致になるはず</t>
+  </si>
+  <si>
+    <t>その他: 候補にないDPC（先頭6桁から違う）</t>
   </si>
   <si>
     <t>060180xx99x0xx</t>
@@ -736,7 +751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763173E4-2481-4D5A-BA3D-D84C65867B8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590CB8D3-D701-41D5-B404-69DA4D28A35E}">
   <dimension ref="A1:E177"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2343,10 +2358,10 @@
         <v>46205</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
@@ -2377,7 +2392,7 @@
         <v>46204</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E97" s="3">
         <v>39039</v>
@@ -2530,7 +2545,7 @@
         <v>46213</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E106" s="3">
         <v>43679</v>
@@ -2581,7 +2596,7 @@
         <v>46211</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E109" s="3">
         <v>30020</v>
@@ -2849,7 +2864,7 @@
         <v>46211</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E125" s="3">
         <v>27372</v>
@@ -2900,9 +2915,11 @@
         <v>46219</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E128" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="E128" s="3">
+        <v>46536</v>
+      </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129">
@@ -2915,7 +2932,7 @@
         <v>46228</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E129" s="3">
         <v>54396</v>
@@ -2949,7 +2966,7 @@
         <v>46214</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E131" s="3">
         <v>26548</v>
@@ -2983,7 +3000,7 @@
         <v>46217</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E133" s="3">
         <v>26116</v>
@@ -3051,11 +3068,9 @@
         <v>46226</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E137" s="3">
-        <v>45164</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E137" s="3"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138">
@@ -3068,7 +3083,7 @@
         <v>46226</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E138" s="3">
         <v>41554</v>
@@ -3136,7 +3151,7 @@
         <v>46216</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E142" s="3">
         <v>22905</v>
@@ -3204,7 +3219,7 @@
         <v>46227</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E146" s="3">
         <v>40776</v>
@@ -3221,7 +3236,7 @@
         <v>46216</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E147" s="3">
         <v>18640</v>
@@ -3238,7 +3253,7 @@
         <v>46225</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E148" s="3">
         <v>35826</v>
@@ -3255,7 +3270,7 @@
         <v>46224</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E149" s="3">
         <v>31865</v>
@@ -3289,7 +3304,7 @@
         <v>46224</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E151" s="3">
         <v>33337</v>
@@ -3493,7 +3508,7 @@
         <v>46230</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E163" s="3">
         <v>30020</v>
@@ -3610,7 +3625,7 @@
         <v>46234</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E170" s="3">
         <v>30720</v>
@@ -3644,7 +3659,7 @@
         <v>46234</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E172" s="3">
         <v>27074</v>
@@ -3712,7 +3727,7 @@
         <v>46231</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E176" s="3">
         <v>14288</v>
@@ -3729,7 +3744,7 @@
         <v>46234</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E177" s="3">
         <v>25926</v>
@@ -3742,21 +3757,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EE6F65-599F-451C-AC56-15FFA3824453}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2295F436-F459-4592-B1A8-8A62A977B3B3}">
   <dimension ref="A1:K177"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="54.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="73.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -3767,31 +3782,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -3802,7 +3817,7 @@
         <v>46128</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -3811,7 +3826,7 @@
         <v>108280</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G2">
         <v>123921</v>
@@ -3820,10 +3835,10 @@
         <v>0.85</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -3834,7 +3849,7 @@
         <v>46143</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
@@ -3849,10 +3864,10 @@
         <v>148972</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
@@ -3863,7 +3878,7 @@
         <v>46150</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -3881,13 +3896,13 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -3898,7 +3913,7 @@
         <v>46152</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -3913,10 +3928,10 @@
         <v>74892</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
@@ -3927,7 +3942,7 @@
         <v>46154</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
@@ -3945,10 +3960,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
@@ -3959,7 +3974,7 @@
         <v>46154</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -3974,10 +3989,10 @@
         <v>108842</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
@@ -3988,7 +4003,7 @@
         <v>46155</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>11</v>
@@ -4003,10 +4018,10 @@
         <v>64664</v>
       </c>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -4017,7 +4032,7 @@
         <v>46157</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -4032,10 +4047,10 @@
         <v>45368</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
@@ -4046,7 +4061,7 @@
         <v>46159</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
@@ -4061,10 +4076,10 @@
         <v>49076</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
@@ -4075,7 +4090,7 @@
         <v>46159</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
@@ -4090,10 +4105,10 @@
         <v>41556</v>
       </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -4104,7 +4119,7 @@
         <v>46160</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>13</v>
@@ -4119,10 +4134,10 @@
         <v>47094</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
@@ -4133,7 +4148,7 @@
         <v>46160</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>11</v>
@@ -4148,10 +4163,10 @@
         <v>43214</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -4162,7 +4177,7 @@
         <v>46161</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>14</v>
@@ -4177,10 +4192,10 @@
         <v>68095</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
@@ -4191,7 +4206,7 @@
         <v>46161</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>15</v>
@@ -4206,10 +4221,10 @@
         <v>42185</v>
       </c>
       <c r="I15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
@@ -4220,7 +4235,7 @@
         <v>46162</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>16</v>
@@ -4235,10 +4250,10 @@
         <v>39355</v>
       </c>
       <c r="I16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
@@ -4249,7 +4264,7 @@
         <v>46162</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>17</v>
@@ -4264,10 +4279,10 @@
         <v>41864</v>
       </c>
       <c r="I17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
@@ -4278,7 +4293,7 @@
         <v>46163</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>18</v>
@@ -4293,10 +4308,10 @@
         <v>44815</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
@@ -4307,7 +4322,7 @@
         <v>46164</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>11</v>
@@ -4322,10 +4337,10 @@
         <v>29564</v>
       </c>
       <c r="I19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
@@ -4336,7 +4351,7 @@
         <v>46164</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>19</v>
@@ -4348,10 +4363,13 @@
         <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="J20" t="s">
+        <v>87</v>
       </c>
       <c r="K20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
@@ -4362,7 +4380,7 @@
         <v>46164</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>20</v>
@@ -4377,10 +4395,10 @@
         <v>65213</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
@@ -4391,7 +4409,7 @@
         <v>46165</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>21</v>
@@ -4409,10 +4427,10 @@
         <v>0.75</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
@@ -4423,7 +4441,7 @@
         <v>46165</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>9</v>
@@ -4438,10 +4456,10 @@
         <v>32352</v>
       </c>
       <c r="I23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
@@ -4452,7 +4470,7 @@
         <v>46165</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>22</v>
@@ -4467,10 +4485,10 @@
         <v>95576</v>
       </c>
       <c r="I24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
@@ -4481,7 +4499,7 @@
         <v>46165</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>23</v>
@@ -4496,10 +4514,10 @@
         <v>29339</v>
       </c>
       <c r="I25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
@@ -4510,7 +4528,7 @@
         <v>46167</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>12</v>
@@ -4525,10 +4543,10 @@
         <v>66334</v>
       </c>
       <c r="I26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
@@ -4539,7 +4557,7 @@
         <v>46167</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>24</v>
@@ -4557,10 +4575,10 @@
         <v>0.7</v>
       </c>
       <c r="I27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
@@ -4571,7 +4589,7 @@
         <v>46167</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>5</v>
@@ -4586,10 +4604,10 @@
         <v>32788</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
@@ -4600,7 +4618,7 @@
         <v>46167</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>25</v>
@@ -4618,10 +4636,10 @@
         <v>0.45</v>
       </c>
       <c r="I29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
@@ -4632,7 +4650,7 @@
         <v>46168</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>26</v>
@@ -4647,10 +4665,10 @@
         <v>82512</v>
       </c>
       <c r="I30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
@@ -4661,7 +4679,7 @@
         <v>46168</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>27</v>
@@ -4676,10 +4694,10 @@
         <v>26486</v>
       </c>
       <c r="I31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
@@ -4690,7 +4708,7 @@
         <v>46168</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>28</v>
@@ -4705,10 +4723,10 @@
         <v>24768</v>
       </c>
       <c r="I32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
@@ -4719,7 +4737,7 @@
         <v>46169</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>11</v>
@@ -4734,10 +4752,10 @@
         <v>33464</v>
       </c>
       <c r="I33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
@@ -4748,7 +4766,7 @@
         <v>46169</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>29</v>
@@ -4763,10 +4781,10 @@
         <v>47042</v>
       </c>
       <c r="I34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
@@ -4777,7 +4795,7 @@
         <v>46169</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>30</v>
@@ -4795,10 +4813,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
@@ -4809,7 +4827,7 @@
         <v>46169</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>28</v>
@@ -4824,10 +4842,10 @@
         <v>18042</v>
       </c>
       <c r="I36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
@@ -4838,7 +4856,7 @@
         <v>46170</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>9</v>
@@ -4856,13 +4874,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
@@ -4873,7 +4891,7 @@
         <v>46170</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>11</v>
@@ -4888,10 +4906,10 @@
         <v>29564</v>
       </c>
       <c r="I38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
@@ -4902,7 +4920,7 @@
         <v>46171</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>31</v>
@@ -4920,13 +4938,13 @@
         <v>0.45</v>
       </c>
       <c r="I39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
@@ -4937,7 +4955,7 @@
         <v>46171</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>12</v>
@@ -4955,10 +4973,10 @@
         <v>0.45</v>
       </c>
       <c r="I40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
@@ -4969,7 +4987,7 @@
         <v>46172</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>8</v>
@@ -4984,10 +5002,10 @@
         <v>61984</v>
       </c>
       <c r="I41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
@@ -4998,7 +5016,7 @@
         <v>46172</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>11</v>
@@ -5013,10 +5031,10 @@
         <v>21764</v>
       </c>
       <c r="I42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
@@ -5027,7 +5045,7 @@
         <v>46173</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
@@ -5042,10 +5060,10 @@
         <v>54812</v>
       </c>
       <c r="I43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
@@ -5056,7 +5074,7 @@
         <v>46173</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>32</v>
@@ -5071,10 +5089,10 @@
         <v>50711</v>
       </c>
       <c r="I44" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
@@ -5085,7 +5103,7 @@
         <v>46173</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>33</v>
@@ -5100,10 +5118,10 @@
         <v>44154</v>
       </c>
       <c r="I45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
@@ -5114,7 +5132,7 @@
         <v>46174</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>28</v>
@@ -5129,10 +5147,10 @@
         <v>15800</v>
       </c>
       <c r="I46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
@@ -5143,7 +5161,7 @@
         <v>46175</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>34</v>
@@ -5158,10 +5176,10 @@
         <v>38927</v>
       </c>
       <c r="I47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J47" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
@@ -5172,7 +5190,7 @@
         <v>46175</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>35</v>
@@ -5187,10 +5205,10 @@
         <v>45163</v>
       </c>
       <c r="I48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
@@ -5201,7 +5219,7 @@
         <v>46175</v>
       </c>
       <c r="C49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>36</v>
@@ -5216,10 +5234,10 @@
         <v>37430</v>
       </c>
       <c r="I49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J49" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
@@ -5230,7 +5248,7 @@
         <v>46176</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
@@ -5245,10 +5263,10 @@
         <v>62016</v>
       </c>
       <c r="I50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
@@ -5259,7 +5277,7 @@
         <v>46176</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>12</v>
@@ -5274,10 +5292,10 @@
         <v>39650</v>
       </c>
       <c r="I51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
@@ -5288,7 +5306,7 @@
         <v>46176</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>37</v>
@@ -5303,10 +5321,10 @@
         <v>48036</v>
       </c>
       <c r="I52" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J52" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
@@ -5317,7 +5335,7 @@
         <v>46176</v>
       </c>
       <c r="C53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>38</v>
@@ -5335,13 +5353,13 @@
         <v>0.7</v>
       </c>
       <c r="I53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
@@ -5352,7 +5370,7 @@
         <v>46176</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>39</v>
@@ -5367,10 +5385,10 @@
         <v>35296</v>
       </c>
       <c r="I54" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J54" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
@@ -5381,7 +5399,7 @@
         <v>46176</v>
       </c>
       <c r="C55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>40</v>
@@ -5399,13 +5417,13 @@
         <v>0.5</v>
       </c>
       <c r="I55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
@@ -5416,7 +5434,7 @@
         <v>46177</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>13</v>
@@ -5431,10 +5449,10 @@
         <v>53358</v>
       </c>
       <c r="I56" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J56" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
@@ -5445,16 +5463,19 @@
         <v>46177</v>
       </c>
       <c r="C57" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I57" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J57" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
@@ -5465,7 +5486,7 @@
         <v>46177</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>42</v>
@@ -5480,10 +5501,10 @@
         <v>21728</v>
       </c>
       <c r="I58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J58" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
@@ -5494,7 +5515,7 @@
         <v>46178</v>
       </c>
       <c r="C59" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>9</v>
@@ -5509,10 +5530,10 @@
         <v>26811</v>
       </c>
       <c r="I59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
@@ -5523,7 +5544,7 @@
         <v>46179</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
@@ -5538,10 +5559,10 @@
         <v>38349</v>
       </c>
       <c r="I60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
@@ -5552,7 +5573,7 @@
         <v>46181</v>
       </c>
       <c r="C61" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>41</v>
@@ -5564,7 +5585,10 @@
         <v>38742</v>
       </c>
       <c r="I61" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J61" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
@@ -5575,7 +5599,7 @@
         <v>46181</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>11</v>
@@ -5590,10 +5614,10 @@
         <v>27614</v>
       </c>
       <c r="I62" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J62" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.45">
@@ -5604,7 +5628,7 @@
         <v>46181</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>43</v>
@@ -5619,10 +5643,10 @@
         <v>58100</v>
       </c>
       <c r="I63" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.45">
@@ -5633,7 +5657,7 @@
         <v>46183</v>
       </c>
       <c r="C64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>12</v>
@@ -5648,10 +5672,10 @@
         <v>39650</v>
       </c>
       <c r="I64" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J64" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
@@ -5662,7 +5686,7 @@
         <v>46183</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>44</v>
@@ -5677,10 +5701,10 @@
         <v>54198</v>
       </c>
       <c r="I65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
@@ -5691,16 +5715,19 @@
         <v>46183</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I66" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J66" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
@@ -5711,7 +5738,7 @@
         <v>46184</v>
       </c>
       <c r="C67" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>28</v>
@@ -5726,10 +5753,10 @@
         <v>15800</v>
       </c>
       <c r="I67" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
@@ -5740,7 +5767,7 @@
         <v>46184</v>
       </c>
       <c r="C68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>44</v>
@@ -5755,10 +5782,10 @@
         <v>42432</v>
       </c>
       <c r="I68" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J68" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
@@ -5769,7 +5796,7 @@
         <v>46184</v>
       </c>
       <c r="C69" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>41</v>
@@ -5781,7 +5808,10 @@
         <v>18042</v>
       </c>
       <c r="I69" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J69" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
@@ -5792,7 +5822,7 @@
         <v>46184</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>45</v>
@@ -5801,7 +5831,7 @@
         <v>47898</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G70">
         <v>45618</v>
@@ -5810,10 +5840,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J70" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
@@ -5824,7 +5854,7 @@
         <v>46184</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>11</v>
@@ -5839,10 +5869,10 @@
         <v>33464</v>
       </c>
       <c r="I71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
@@ -5853,7 +5883,7 @@
         <v>46185</v>
       </c>
       <c r="C72" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>9</v>
@@ -5868,10 +5898,10 @@
         <v>47128</v>
       </c>
       <c r="I72" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J72" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
@@ -5882,7 +5912,7 @@
         <v>46185</v>
       </c>
       <c r="C73" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>17</v>
@@ -5897,10 +5927,10 @@
         <v>48131</v>
       </c>
       <c r="I73" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J73" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
@@ -5911,7 +5941,7 @@
         <v>46186</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>28</v>
@@ -5926,10 +5956,10 @@
         <v>28578</v>
       </c>
       <c r="I74" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
@@ -5940,7 +5970,7 @@
         <v>46187</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>46</v>
@@ -5958,10 +5988,10 @@
         <v>0.5</v>
       </c>
       <c r="I75" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
@@ -5972,7 +6002,7 @@
         <v>46188</v>
       </c>
       <c r="C76" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
@@ -5987,10 +6017,10 @@
         <v>27614</v>
       </c>
       <c r="I76" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J76" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
@@ -6001,7 +6031,7 @@
         <v>46188</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>47</v>
@@ -6019,10 +6049,10 @@
         <v>0.78</v>
       </c>
       <c r="I77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
@@ -6033,7 +6063,7 @@
         <v>46188</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>10</v>
@@ -6048,10 +6078,10 @@
         <v>51210</v>
       </c>
       <c r="I78" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J78" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
@@ -6062,7 +6092,7 @@
         <v>46188</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
@@ -6077,10 +6107,10 @@
         <v>53011</v>
       </c>
       <c r="I79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
@@ -6091,7 +6121,7 @@
         <v>46188</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>48</v>
@@ -6106,13 +6136,13 @@
         <v>56003</v>
       </c>
       <c r="I80" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J80" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>6031532</v>
       </c>
@@ -6120,7 +6150,7 @@
         <v>46188</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>12</v>
@@ -6135,13 +6165,13 @@
         <v>49180</v>
       </c>
       <c r="I81" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J81" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>6705226</v>
       </c>
@@ -6149,7 +6179,7 @@
         <v>46188</v>
       </c>
       <c r="C82" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>5</v>
@@ -6167,13 +6197,13 @@
         <v>0.75</v>
       </c>
       <c r="I82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J82" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>6783496</v>
       </c>
@@ -6181,7 +6211,7 @@
         <v>46189</v>
       </c>
       <c r="C83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>41</v>
@@ -6193,10 +6223,13 @@
         <v>54898</v>
       </c>
       <c r="I83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+      <c r="J83" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>6823288</v>
       </c>
@@ -6204,7 +6237,7 @@
         <v>46189</v>
       </c>
       <c r="C84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>12</v>
@@ -6219,13 +6252,13 @@
         <v>45368</v>
       </c>
       <c r="I84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J84" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>6841363</v>
       </c>
@@ -6233,7 +6266,7 @@
         <v>46189</v>
       </c>
       <c r="C85" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>14</v>
@@ -6248,13 +6281,13 @@
         <v>44743</v>
       </c>
       <c r="I85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>7006972</v>
       </c>
@@ -6262,7 +6295,7 @@
         <v>46189</v>
       </c>
       <c r="C86" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>41</v>
@@ -6274,10 +6307,13 @@
         <v>57775</v>
       </c>
       <c r="I86" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+      <c r="J86" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>7007241</v>
       </c>
@@ -6285,7 +6321,7 @@
         <v>46189</v>
       </c>
       <c r="C87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>29</v>
@@ -6300,13 +6336,13 @@
         <v>47042</v>
       </c>
       <c r="I87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>224181</v>
       </c>
@@ -6314,7 +6350,7 @@
         <v>46190</v>
       </c>
       <c r="C88" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>48</v>
@@ -6329,13 +6365,13 @@
         <v>14867</v>
       </c>
       <c r="I88" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J88" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>3046984</v>
       </c>
@@ -6343,7 +6379,7 @@
         <v>46190</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>14</v>
@@ -6358,13 +6394,13 @@
         <v>66149</v>
       </c>
       <c r="I89" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J89" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>4348909</v>
       </c>
@@ -6372,7 +6408,7 @@
         <v>46190</v>
       </c>
       <c r="C90" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>49</v>
@@ -6387,13 +6423,13 @@
         <v>16140</v>
       </c>
       <c r="I90" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J90" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>7007645</v>
       </c>
@@ -6401,7 +6437,7 @@
         <v>46190</v>
       </c>
       <c r="C91" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>9</v>
@@ -6416,13 +6452,13 @@
         <v>26811</v>
       </c>
       <c r="I91" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J91" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>2420963</v>
       </c>
@@ -6430,7 +6466,7 @@
         <v>46191</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>48</v>
@@ -6448,13 +6484,13 @@
         <v>0.4</v>
       </c>
       <c r="I92" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J92" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>2581999</v>
       </c>
@@ -6462,7 +6498,7 @@
         <v>46191</v>
       </c>
       <c r="C93" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>50</v>
@@ -6477,13 +6513,13 @@
         <v>13302</v>
       </c>
       <c r="I93" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J93" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>5621102</v>
       </c>
@@ -6491,7 +6527,7 @@
         <v>46191</v>
       </c>
       <c r="C94" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>9</v>
@@ -6506,13 +6542,13 @@
         <v>28658</v>
       </c>
       <c r="I94" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J94" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>7002013</v>
       </c>
@@ -6520,13 +6556,13 @@
         <v>46191</v>
       </c>
       <c r="C95" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E95" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>17</v>
@@ -6535,10 +6571,16 @@
         <v>39775</v>
       </c>
       <c r="I95" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+      <c r="J95" t="s">
+        <v>96</v>
+      </c>
+      <c r="K95" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>7007760</v>
       </c>
@@ -6546,7 +6588,7 @@
         <v>46191</v>
       </c>
       <c r="C96" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>36</v>
@@ -6561,10 +6603,10 @@
         <v>60854</v>
       </c>
       <c r="I96" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J96" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
@@ -6575,10 +6617,10 @@
         <v>46192</v>
       </c>
       <c r="C97" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E97">
         <v>39039</v>
@@ -6593,10 +6635,10 @@
         <v>0.42</v>
       </c>
       <c r="I97" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J97" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
@@ -6607,7 +6649,7 @@
         <v>46192</v>
       </c>
       <c r="C98" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>35</v>
@@ -6622,10 +6664,10 @@
         <v>48997</v>
       </c>
       <c r="I98" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J98" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
@@ -6636,7 +6678,7 @@
         <v>46192</v>
       </c>
       <c r="C99" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>35</v>
@@ -6651,10 +6693,10 @@
         <v>64333</v>
       </c>
       <c r="I99" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J99" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
@@ -6665,7 +6707,7 @@
         <v>46193</v>
       </c>
       <c r="C100" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>13</v>
@@ -6680,10 +6722,10 @@
         <v>34566</v>
       </c>
       <c r="I100" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J100" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
@@ -6694,7 +6736,7 @@
         <v>46193</v>
       </c>
       <c r="C101" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>13</v>
@@ -6709,10 +6751,10 @@
         <v>38742</v>
       </c>
       <c r="I101" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J101" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
@@ -6723,7 +6765,7 @@
         <v>46193</v>
       </c>
       <c r="C102" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>12</v>
@@ -6738,10 +6780,10 @@
         <v>45368</v>
       </c>
       <c r="I102" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J102" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
@@ -6752,7 +6794,7 @@
         <v>46194</v>
       </c>
       <c r="C103" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>30</v>
@@ -6770,10 +6812,10 @@
         <v>0.8</v>
       </c>
       <c r="I103" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J103" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
@@ -6784,7 +6826,7 @@
         <v>46195</v>
       </c>
       <c r="C104" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>11</v>
@@ -6799,10 +6841,10 @@
         <v>29564</v>
       </c>
       <c r="I104" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J104" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
@@ -6813,7 +6855,7 @@
         <v>46196</v>
       </c>
       <c r="C105" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>5</v>
@@ -6831,10 +6873,10 @@
         <v>0.6</v>
       </c>
       <c r="I105" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J105" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
@@ -6845,10 +6887,10 @@
         <v>46196</v>
       </c>
       <c r="C106" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E106">
         <v>43679</v>
@@ -6863,10 +6905,10 @@
         <v>0.6</v>
       </c>
       <c r="I106" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J106" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
@@ -6877,7 +6919,7 @@
         <v>46197</v>
       </c>
       <c r="C107" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>30</v>
@@ -6895,10 +6937,10 @@
         <v>0.72</v>
       </c>
       <c r="I107" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J107" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
@@ -6909,7 +6951,7 @@
         <v>46197</v>
       </c>
       <c r="C108" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>8</v>
@@ -6924,10 +6966,10 @@
         <v>85956</v>
       </c>
       <c r="I108" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J108" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
@@ -6938,25 +6980,25 @@
         <v>46198</v>
       </c>
       <c r="C109" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E109">
         <v>30020</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G109">
         <v>30020</v>
       </c>
       <c r="I109" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J109" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
@@ -6967,7 +7009,7 @@
         <v>46199</v>
       </c>
       <c r="C110" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>12</v>
@@ -6982,10 +7024,10 @@
         <v>77770</v>
       </c>
       <c r="I110" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J110" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
@@ -6996,7 +7038,7 @@
         <v>46199</v>
       </c>
       <c r="C111" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>33</v>
@@ -7011,10 +7053,10 @@
         <v>49257</v>
       </c>
       <c r="I111" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J111" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
@@ -7025,7 +7067,7 @@
         <v>46199</v>
       </c>
       <c r="C112" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>35</v>
@@ -7040,10 +7082,10 @@
         <v>62416</v>
       </c>
       <c r="I112" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J112" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.45">
@@ -7054,7 +7096,7 @@
         <v>46200</v>
       </c>
       <c r="C113" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>13</v>
@@ -7069,10 +7111,10 @@
         <v>38742</v>
       </c>
       <c r="I113" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J113" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.45">
@@ -7083,7 +7125,7 @@
         <v>46200</v>
       </c>
       <c r="C114" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>27</v>
@@ -7098,10 +7140,10 @@
         <v>26486</v>
       </c>
       <c r="I114" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J114" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.45">
@@ -7112,7 +7154,7 @@
         <v>46200</v>
       </c>
       <c r="C115" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>41</v>
@@ -7124,7 +7166,10 @@
         <v>34513</v>
       </c>
       <c r="I115" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J115" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.45">
@@ -7135,7 +7180,7 @@
         <v>46201</v>
       </c>
       <c r="C116" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>28</v>
@@ -7150,10 +7195,10 @@
         <v>18042</v>
       </c>
       <c r="I116" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J116" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.45">
@@ -7164,7 +7209,7 @@
         <v>46201</v>
       </c>
       <c r="C117" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>48</v>
@@ -7182,10 +7227,10 @@
         <v>0.7</v>
       </c>
       <c r="I117" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J117" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.45">
@@ -7196,7 +7241,7 @@
         <v>46202</v>
       </c>
       <c r="C118" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>28</v>
@@ -7211,10 +7256,10 @@
         <v>15800</v>
       </c>
       <c r="I118" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J118" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.45">
@@ -7225,7 +7270,7 @@
         <v>46202</v>
       </c>
       <c r="C119" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>29</v>
@@ -7240,10 +7285,10 @@
         <v>45121</v>
       </c>
       <c r="I119" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J119" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.45">
@@ -7254,16 +7299,19 @@
         <v>46202</v>
       </c>
       <c r="C120" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I120" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J120" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.45">
@@ -7274,7 +7322,7 @@
         <v>46203</v>
       </c>
       <c r="C121" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>11</v>
@@ -7289,10 +7337,10 @@
         <v>51014</v>
       </c>
       <c r="I121" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J121" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.45">
@@ -7303,7 +7351,7 @@
         <v>46203</v>
       </c>
       <c r="C122" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>28</v>
@@ -7318,10 +7366,10 @@
         <v>20284</v>
       </c>
       <c r="I122" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J122" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.45">
@@ -7332,7 +7380,7 @@
         <v>46203</v>
       </c>
       <c r="C123" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>48</v>
@@ -7347,10 +7395,10 @@
         <v>17479</v>
       </c>
       <c r="I123" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J123" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.45">
@@ -7361,7 +7409,7 @@
         <v>46203</v>
       </c>
       <c r="C124" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>48</v>
@@ -7376,10 +7424,10 @@
         <v>29363</v>
       </c>
       <c r="I124" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J124" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.45">
@@ -7390,10 +7438,10 @@
         <v>46203</v>
       </c>
       <c r="C125" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E125">
         <v>27372</v>
@@ -7408,13 +7456,13 @@
         <v>0.45</v>
       </c>
       <c r="I125" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J125" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K125" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.45">
@@ -7425,7 +7473,7 @@
         <v>46203</v>
       </c>
       <c r="C126" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>48</v>
@@ -7440,10 +7488,10 @@
         <v>27143</v>
       </c>
       <c r="I126" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J126" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.45">
@@ -7454,7 +7502,7 @@
         <v>46204</v>
       </c>
       <c r="C127" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>27</v>
@@ -7469,10 +7517,10 @@
         <v>26486</v>
       </c>
       <c r="I127" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J127" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.45">
@@ -7483,19 +7531,28 @@
         <v>46204</v>
       </c>
       <c r="C128" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="E128">
+        <v>46536</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="G128">
         <v>46536</v>
       </c>
       <c r="I128" t="s">
-        <v>85</v>
+        <v>99</v>
+      </c>
+      <c r="J128" t="s">
+        <v>96</v>
+      </c>
+      <c r="K128" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.45">
@@ -7506,25 +7563,25 @@
         <v>46204</v>
       </c>
       <c r="C129" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E129">
         <v>54396</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G129">
         <v>54396</v>
       </c>
       <c r="I129" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J129" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.45">
@@ -7535,7 +7592,7 @@
         <v>46205</v>
       </c>
       <c r="C130" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>48</v>
@@ -7553,10 +7610,10 @@
         <v>0.78</v>
       </c>
       <c r="I130" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J130" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.45">
@@ -7567,10 +7624,10 @@
         <v>46205</v>
       </c>
       <c r="C131" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E131">
         <v>26548</v>
@@ -7585,10 +7642,10 @@
         <v>0.6</v>
       </c>
       <c r="I131" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J131" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.45">
@@ -7599,7 +7656,7 @@
         <v>46205</v>
       </c>
       <c r="C132" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>28</v>
@@ -7614,10 +7671,10 @@
         <v>32388</v>
       </c>
       <c r="I132" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J132" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.45">
@@ -7628,10 +7685,10 @@
         <v>46205</v>
       </c>
       <c r="C133" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>26116</v>
@@ -7646,10 +7703,10 @@
         <v>0.8</v>
       </c>
       <c r="I133" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J133" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.45">
@@ -7660,7 +7717,7 @@
         <v>46205</v>
       </c>
       <c r="C134" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>8</v>
@@ -7675,10 +7732,10 @@
         <v>56452</v>
       </c>
       <c r="I134" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J134" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.45">
@@ -7689,7 +7746,7 @@
         <v>46205</v>
       </c>
       <c r="C135" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>15</v>
@@ -7707,10 +7764,10 @@
         <v>0.7</v>
       </c>
       <c r="I135" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J135" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.45">
@@ -7721,7 +7778,7 @@
         <v>46206</v>
       </c>
       <c r="C136" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>8</v>
@@ -7736,10 +7793,10 @@
         <v>52764</v>
       </c>
       <c r="I136" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J136" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.45">
@@ -7750,13 +7807,10 @@
         <v>46207</v>
       </c>
       <c r="C137" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E137">
-        <v>45164</v>
+        <v>61</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>11</v>
@@ -7765,13 +7819,13 @@
         <v>45164</v>
       </c>
       <c r="I137" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J137" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K137" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.45">
@@ -7782,25 +7836,25 @@
         <v>46207</v>
       </c>
       <c r="C138" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E138">
         <v>41554</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G138">
         <v>41554</v>
       </c>
       <c r="I138" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J138" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.45">
@@ -7811,7 +7865,7 @@
         <v>46207</v>
       </c>
       <c r="C139" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>13</v>
@@ -7826,10 +7880,10 @@
         <v>34566</v>
       </c>
       <c r="I139" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J139" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.45">
@@ -7840,7 +7894,7 @@
         <v>46207</v>
       </c>
       <c r="C140" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>46</v>
@@ -7858,10 +7912,10 @@
         <v>0.45</v>
       </c>
       <c r="I140" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J140" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.45">
@@ -7872,7 +7926,7 @@
         <v>46209</v>
       </c>
       <c r="C141" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>27</v>
@@ -7887,10 +7941,10 @@
         <v>24501</v>
       </c>
       <c r="I141" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J141" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.45">
@@ -7901,25 +7955,25 @@
         <v>46209</v>
       </c>
       <c r="C142" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E142">
         <v>22905</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G142">
         <v>22905</v>
       </c>
       <c r="I142" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J142" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.45">
@@ -7930,7 +7984,7 @@
         <v>46209</v>
       </c>
       <c r="C143" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>35</v>
@@ -7948,10 +8002,10 @@
         <v>0.7</v>
       </c>
       <c r="I143" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J143" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.45">
@@ -7962,7 +8016,7 @@
         <v>46209</v>
       </c>
       <c r="C144" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>16</v>
@@ -7977,10 +8031,10 @@
         <v>44881</v>
       </c>
       <c r="I144" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J144" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.45">
@@ -7991,7 +8045,7 @@
         <v>46209</v>
       </c>
       <c r="C145" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>12</v>
@@ -8006,10 +8060,10 @@
         <v>56804</v>
       </c>
       <c r="I145" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J145" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.45">
@@ -8020,25 +8074,25 @@
         <v>46210</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E146">
         <v>40776</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G146">
         <v>40776</v>
       </c>
       <c r="I146" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J146" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.45">
@@ -8049,25 +8103,25 @@
         <v>46210</v>
       </c>
       <c r="C147" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>18640</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G147">
         <v>18640</v>
       </c>
       <c r="I147" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J147" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.45">
@@ -8078,10 +8132,10 @@
         <v>46210</v>
       </c>
       <c r="C148" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E148">
         <v>35826</v>
@@ -8096,10 +8150,10 @@
         <v>0.75</v>
       </c>
       <c r="I148" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J148" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.45">
@@ -8110,25 +8164,25 @@
         <v>46210</v>
       </c>
       <c r="C149" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E149">
         <v>31865</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G149">
         <v>31865</v>
       </c>
       <c r="I149" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J149" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.45">
@@ -8139,7 +8193,7 @@
         <v>46211</v>
       </c>
       <c r="C150" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>13</v>
@@ -8154,10 +8208,10 @@
         <v>32109</v>
       </c>
       <c r="I150" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J150" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.45">
@@ -8168,10 +8222,10 @@
         <v>46211</v>
       </c>
       <c r="C151" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E151">
         <v>33337</v>
@@ -8186,10 +8240,10 @@
         <v>0.7</v>
       </c>
       <c r="I151" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J151" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.45">
@@ -8200,7 +8254,7 @@
         <v>46211</v>
       </c>
       <c r="C152" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>28</v>
@@ -8215,10 +8269,10 @@
         <v>26673</v>
       </c>
       <c r="I152" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J152" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.45">
@@ -8229,7 +8283,7 @@
         <v>46212</v>
       </c>
       <c r="C153" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>12</v>
@@ -8244,10 +8298,10 @@
         <v>39650</v>
       </c>
       <c r="I153" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J153" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.45">
@@ -8258,7 +8312,7 @@
         <v>46212</v>
       </c>
       <c r="C154" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>28</v>
@@ -8273,10 +8327,10 @@
         <v>15800</v>
       </c>
       <c r="I154" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J154" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.45">
@@ -8287,7 +8341,7 @@
         <v>46213</v>
       </c>
       <c r="C155" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>5</v>
@@ -8305,13 +8359,13 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J155" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K155" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.45">
@@ -8322,7 +8376,7 @@
         <v>46213</v>
       </c>
       <c r="C156" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>27</v>
@@ -8337,10 +8391,10 @@
         <v>36411</v>
       </c>
       <c r="I156" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J156" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.45">
@@ -8351,7 +8405,7 @@
         <v>46215</v>
       </c>
       <c r="C157" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>5</v>
@@ -8369,13 +8423,13 @@
         <v>0.65</v>
       </c>
       <c r="I157" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J157" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K157" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.45">
@@ -8386,7 +8440,7 @@
         <v>46215</v>
       </c>
       <c r="C158" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>41</v>
@@ -8401,10 +8455,10 @@
         <v>15800</v>
       </c>
       <c r="I158" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J158" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.45">
@@ -8415,7 +8469,7 @@
         <v>46216</v>
       </c>
       <c r="C159" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>15</v>
@@ -8430,10 +8484,10 @@
         <v>44103</v>
       </c>
       <c r="I159" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J159" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.45">
@@ -8444,7 +8498,7 @@
         <v>46216</v>
       </c>
       <c r="C160" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>39</v>
@@ -8459,10 +8513,10 @@
         <v>37202</v>
       </c>
       <c r="I160" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J160" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.45">
@@ -8473,7 +8527,7 @@
         <v>46216</v>
       </c>
       <c r="C161" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>17</v>
@@ -8488,10 +8542,10 @@
         <v>39775</v>
       </c>
       <c r="I161" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J161" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.45">
@@ -8502,7 +8556,7 @@
         <v>46216</v>
       </c>
       <c r="C162" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>21</v>
@@ -8517,10 +8571,10 @@
         <v>38888</v>
       </c>
       <c r="I162" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J162" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.45">
@@ -8531,25 +8585,25 @@
         <v>46217</v>
       </c>
       <c r="C163" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E163">
         <v>30020</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G163">
         <v>30020</v>
       </c>
       <c r="I163" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J163" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.45">
@@ -8560,7 +8614,7 @@
         <v>46217</v>
       </c>
       <c r="C164" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>49</v>
@@ -8575,10 +8629,10 @@
         <v>29104</v>
       </c>
       <c r="I164" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J164" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.45">
@@ -8589,7 +8643,7 @@
         <v>46217</v>
       </c>
       <c r="C165" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>41</v>
@@ -8601,7 +8655,10 @@
         <v>33038</v>
       </c>
       <c r="I165" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J165" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.45">
@@ -8612,7 +8669,7 @@
         <v>46218</v>
       </c>
       <c r="C166" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>36</v>
@@ -8627,10 +8684,10 @@
         <v>31574</v>
       </c>
       <c r="I166" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J166" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.45">
@@ -8641,7 +8698,7 @@
         <v>46218</v>
       </c>
       <c r="C167" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>9</v>
@@ -8656,10 +8713,10 @@
         <v>24964</v>
       </c>
       <c r="I167" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J167" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.45">
@@ -8670,7 +8727,7 @@
         <v>46218</v>
       </c>
       <c r="C168" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>34</v>
@@ -8685,10 +8742,10 @@
         <v>28766</v>
       </c>
       <c r="I168" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J168" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.45">
@@ -8699,7 +8756,7 @@
         <v>46220</v>
       </c>
       <c r="C169" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>21</v>
@@ -8708,7 +8765,7 @@
         <v>33188</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G169">
         <v>33194</v>
@@ -8717,10 +8774,10 @@
         <v>0.7</v>
       </c>
       <c r="I169" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J169" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.45">
@@ -8731,25 +8788,25 @@
         <v>46223</v>
       </c>
       <c r="C170" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E170">
         <v>30720</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G170">
         <v>30720</v>
       </c>
       <c r="I170" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J170" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.45">
@@ -8760,7 +8817,7 @@
         <v>46224</v>
       </c>
       <c r="C171" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>13</v>
@@ -8775,10 +8832,10 @@
         <v>32109</v>
       </c>
       <c r="I171" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J171" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.45">
@@ -8789,25 +8846,25 @@
         <v>46225</v>
       </c>
       <c r="C172" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E172">
         <v>27074</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G172">
         <v>27074</v>
       </c>
       <c r="I172" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J172" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.45">
@@ -8818,7 +8875,7 @@
         <v>46225</v>
       </c>
       <c r="C173" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>9</v>
@@ -8833,10 +8890,10 @@
         <v>24964</v>
       </c>
       <c r="I173" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J173" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.45">
@@ -8847,7 +8904,7 @@
         <v>46226</v>
       </c>
       <c r="C174" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>11</v>
@@ -8862,10 +8919,10 @@
         <v>21764</v>
       </c>
       <c r="I174" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J174" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.45">
@@ -8876,7 +8933,7 @@
         <v>46226</v>
       </c>
       <c r="C175" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>48</v>
@@ -8891,10 +8948,10 @@
         <v>22703</v>
       </c>
       <c r="I175" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J175" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.45">
@@ -8905,10 +8962,10 @@
         <v>46226</v>
       </c>
       <c r="C176" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E176">
         <v>14288</v>
@@ -8923,13 +8980,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J176" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K176" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
@@ -8940,25 +8997,25 @@
         <v>46227</v>
       </c>
       <c r="C177" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E177">
         <v>25926</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G177">
         <v>25926</v>
       </c>
       <c r="I177" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J177" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Flow/202609/2026-09-25/AIDPC_アウトプットファイル設計/input/テスト用患者一覧_176件.xlsx
+++ b/Flow/202609/2026-09-25/AIDPC_アウトプットファイル設計/input/テスト用患者一覧_176件.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juny4\Desktop\appl\git\aipm_v0\Flow\202609\2026-09-25\AIDPC_アウトプットファイル設計\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AF99A33-2D91-4288-9706-D70C0AE8E3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59463C80-31CC-4BBB-A9C2-A3AFBD5F3074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1056" yWindow="960" windowWidth="29112" windowHeight="14940" xr2:uid="{2DC5158F-559B-40CB-8CC8-56339E123BBD}"/>
+    <workbookView xWindow="888" yWindow="996" windowWidth="29112" windowHeight="14844" xr2:uid="{2DC5158F-559B-40CB-8CC8-56339E123BBD}"/>
   </bookViews>
   <sheets>
     <sheet name="患者一覧" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="118">
   <si>
     <t>患者番号</t>
   </si>
@@ -362,6 +362,24 @@
   </si>
   <si>
     <t>070510xx99xxxx</t>
+  </si>
+  <si>
+    <t>一覧の点数</t>
+  </si>
+  <si>
+    <t>期待: 取り込み後の点数</t>
+  </si>
+  <si>
+    <t>記載</t>
+  </si>
+  <si>
+    <t>空（点数表から計算）</t>
+  </si>
+  <si>
+    <t>在院日数が入院日Ⅲを超えるため、入院日Ⅲまでの合計で計算</t>
+  </si>
+  <si>
+    <t>空（計算できず未設定）</t>
   </si>
 </sst>
 </file>
@@ -369,7 +387,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -426,7 +444,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -842,9 +860,7 @@
       <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="3">
-        <v>74892</v>
-      </c>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -876,9 +892,7 @@
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="3">
-        <v>108842</v>
-      </c>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -893,9 +907,7 @@
       <c r="D8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="3">
-        <v>64664</v>
-      </c>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -927,9 +939,7 @@
       <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="3">
-        <v>49076</v>
-      </c>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -944,9 +954,7 @@
       <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="3">
-        <v>41556</v>
-      </c>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -978,9 +986,7 @@
       <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="3">
-        <v>43214</v>
-      </c>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -995,9 +1001,7 @@
       <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="3">
-        <v>68095</v>
-      </c>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -1012,9 +1016,7 @@
       <c r="D15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="3">
-        <v>42185</v>
-      </c>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -1046,9 +1048,7 @@
       <c r="D17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="3">
-        <v>41864</v>
-      </c>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18">
@@ -1063,9 +1063,7 @@
       <c r="D18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="3">
-        <v>44815</v>
-      </c>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19">
@@ -1080,9 +1078,7 @@
       <c r="D19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="3">
-        <v>29564</v>
-      </c>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20">
@@ -1114,9 +1110,7 @@
       <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="3">
-        <v>65213</v>
-      </c>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22">
@@ -1131,9 +1125,7 @@
       <c r="D22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="3">
-        <v>46488</v>
-      </c>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23">
@@ -1148,9 +1140,7 @@
       <c r="D23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="3">
-        <v>32352</v>
-      </c>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24">
@@ -1165,9 +1155,7 @@
       <c r="D24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="3">
-        <v>95576</v>
-      </c>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25">
@@ -1216,9 +1204,7 @@
       <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="3">
-        <v>62218</v>
-      </c>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28">
@@ -1233,9 +1219,7 @@
       <c r="D28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E28" s="3">
-        <v>32788</v>
-      </c>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29">
@@ -1250,9 +1234,7 @@
       <c r="D29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="3">
-        <v>22544</v>
-      </c>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30">
@@ -1267,9 +1249,7 @@
       <c r="D30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="3">
-        <v>82512</v>
-      </c>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31">
@@ -1284,9 +1264,7 @@
       <c r="D31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="3">
-        <v>26486</v>
-      </c>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32">
@@ -1301,9 +1279,7 @@
       <c r="D32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="3">
-        <v>24768</v>
-      </c>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33">
@@ -1318,9 +1294,7 @@
       <c r="D33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="3">
-        <v>33464</v>
-      </c>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34">
@@ -1335,9 +1309,7 @@
       <c r="D34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="3">
-        <v>47042</v>
-      </c>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35">
@@ -1352,9 +1324,7 @@
       <c r="D35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="3">
-        <v>64427</v>
-      </c>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36">
@@ -1369,9 +1339,7 @@
       <c r="D36" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="3">
-        <v>18042</v>
-      </c>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37">
@@ -1403,9 +1371,7 @@
       <c r="D38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="3">
-        <v>29564</v>
-      </c>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39">
@@ -1437,9 +1403,7 @@
       <c r="D40" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="3">
-        <v>35502</v>
-      </c>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41">
@@ -1454,9 +1418,7 @@
       <c r="D41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="3">
-        <v>61984</v>
-      </c>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42">
@@ -1488,9 +1450,7 @@
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="3">
-        <v>54812</v>
-      </c>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44">
@@ -1505,9 +1465,7 @@
       <c r="D44" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E44" s="3">
-        <v>50711</v>
-      </c>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45">
@@ -1522,9 +1480,7 @@
       <c r="D45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E45" s="3">
-        <v>44154</v>
-      </c>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46">
@@ -1539,9 +1495,7 @@
       <c r="D46" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="3">
-        <v>15800</v>
-      </c>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47">
@@ -1573,9 +1527,7 @@
       <c r="D48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="3">
-        <v>45163</v>
-      </c>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49">
@@ -1590,9 +1542,7 @@
       <c r="D49" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="3">
-        <v>37430</v>
-      </c>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50">
@@ -1607,9 +1557,7 @@
       <c r="D50" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="3">
-        <v>62016</v>
-      </c>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51">
@@ -1624,9 +1572,7 @@
       <c r="D51" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E51" s="3">
-        <v>39650</v>
-      </c>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52">
@@ -1641,9 +1587,7 @@
       <c r="D52" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E52" s="3">
-        <v>48036</v>
-      </c>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53">
@@ -1675,9 +1619,7 @@
       <c r="D54" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E54" s="3">
-        <v>35296</v>
-      </c>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55">
@@ -1741,9 +1683,7 @@
       <c r="D58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E58" s="3">
-        <v>21728</v>
-      </c>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59">
@@ -1758,9 +1698,7 @@
       <c r="D59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="3">
-        <v>26811</v>
-      </c>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60">
@@ -1775,9 +1713,7 @@
       <c r="D60" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="3">
-        <v>38349</v>
-      </c>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61">
@@ -1824,9 +1760,7 @@
       <c r="D63" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="3">
-        <v>58100</v>
-      </c>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64">
@@ -1858,9 +1792,7 @@
       <c r="D65" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E65" s="3">
-        <v>54198</v>
-      </c>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66">
@@ -1907,9 +1839,7 @@
       <c r="D68" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E68" s="3">
-        <v>42432</v>
-      </c>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69">
@@ -1939,9 +1869,7 @@
       <c r="D70" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E70" s="3">
-        <v>47898</v>
-      </c>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71">
@@ -1973,9 +1901,7 @@
       <c r="D72" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="3">
-        <v>47128</v>
-      </c>
+      <c r="E72" s="3"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73">
@@ -2041,9 +1967,7 @@
       <c r="D76" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E76" s="3">
-        <v>27614</v>
-      </c>
+      <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77">
@@ -2075,9 +1999,7 @@
       <c r="D78" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E78" s="3">
-        <v>51210</v>
-      </c>
+      <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79">
@@ -2092,9 +2014,7 @@
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="3">
-        <v>53011</v>
-      </c>
+      <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80">
@@ -2109,9 +2029,7 @@
       <c r="D80" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E80" s="3">
-        <v>56003</v>
-      </c>
+      <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81">
@@ -2143,9 +2061,7 @@
       <c r="D82" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E82" s="3">
-        <v>18840</v>
-      </c>
+      <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83">
@@ -2175,9 +2091,7 @@
       <c r="D84" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E84" s="3">
-        <v>45368</v>
-      </c>
+      <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85">
@@ -2192,9 +2106,7 @@
       <c r="D85" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E85" s="3">
-        <v>44743</v>
-      </c>
+      <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86">
@@ -2224,9 +2136,7 @@
       <c r="D87" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E87" s="3">
-        <v>47042</v>
-      </c>
+      <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88">
@@ -2241,9 +2151,7 @@
       <c r="D88" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E88" s="3">
-        <v>14867</v>
-      </c>
+      <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89">
@@ -2292,9 +2200,7 @@
       <c r="D91" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E91" s="3">
-        <v>26811</v>
-      </c>
+      <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92">
@@ -2326,9 +2232,7 @@
       <c r="D93" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E93" s="3">
-        <v>13302</v>
-      </c>
+      <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94">
@@ -2343,9 +2247,7 @@
       <c r="D94" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E94" s="3">
-        <v>28658</v>
-      </c>
+      <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95">
@@ -2377,9 +2279,7 @@
       <c r="D96" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E96" s="3">
-        <v>60854</v>
-      </c>
+      <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97">
@@ -2394,9 +2294,7 @@
       <c r="D97" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E97" s="3">
-        <v>39039</v>
-      </c>
+      <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98">
@@ -2428,9 +2326,7 @@
       <c r="D99" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E99" s="3">
-        <v>64333</v>
-      </c>
+      <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100">
@@ -2445,9 +2341,7 @@
       <c r="D100" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E100" s="3">
-        <v>34566</v>
-      </c>
+      <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101">
@@ -2462,9 +2356,7 @@
       <c r="D101" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E101" s="3">
-        <v>38742</v>
-      </c>
+      <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102">
@@ -2479,9 +2371,7 @@
       <c r="D102" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E102" s="3">
-        <v>45368</v>
-      </c>
+      <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103">
@@ -2496,9 +2386,7 @@
       <c r="D103" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E103" s="3">
-        <v>43065</v>
-      </c>
+      <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104">
@@ -2513,9 +2401,7 @@
       <c r="D104" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E104" s="3">
-        <v>29564</v>
-      </c>
+      <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105">
@@ -2547,9 +2433,7 @@
       <c r="D106" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="3">
-        <v>43679</v>
-      </c>
+      <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107">
@@ -2564,9 +2448,7 @@
       <c r="D107" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E107" s="3">
-        <v>27529</v>
-      </c>
+      <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108">
@@ -2598,9 +2480,7 @@
       <c r="D109" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E109" s="3">
-        <v>30020</v>
-      </c>
+      <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110">
@@ -2615,9 +2495,7 @@
       <c r="D110" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E110" s="3">
-        <v>77770</v>
-      </c>
+      <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111">
@@ -2632,9 +2510,7 @@
       <c r="D111" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E111" s="3">
-        <v>49257</v>
-      </c>
+      <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112">
@@ -2649,9 +2525,7 @@
       <c r="D112" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E112" s="3">
-        <v>62416</v>
-      </c>
+      <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113">
@@ -2666,9 +2540,7 @@
       <c r="D113" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E113" s="3">
-        <v>38742</v>
-      </c>
+      <c r="E113" s="3"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114">
@@ -2715,9 +2587,7 @@
       <c r="D116" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E116" s="3">
-        <v>18042</v>
-      </c>
+      <c r="E116" s="3"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117">
@@ -2732,9 +2602,7 @@
       <c r="D117" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E117" s="3">
-        <v>33803</v>
-      </c>
+      <c r="E117" s="3"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118">
@@ -2749,9 +2617,7 @@
       <c r="D118" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E118" s="3">
-        <v>15800</v>
-      </c>
+      <c r="E118" s="3"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119">
@@ -2766,9 +2632,7 @@
       <c r="D119" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E119" s="3">
-        <v>45121</v>
-      </c>
+      <c r="E119" s="3"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120">
@@ -2798,9 +2662,7 @@
       <c r="D121" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E121" s="3">
-        <v>51014</v>
-      </c>
+      <c r="E121" s="3"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122">
@@ -2815,9 +2677,7 @@
       <c r="D122" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E122" s="3">
-        <v>20284</v>
-      </c>
+      <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123">
@@ -2832,9 +2692,7 @@
       <c r="D123" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E123" s="3">
-        <v>17479</v>
-      </c>
+      <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124">
@@ -2900,9 +2758,7 @@
       <c r="D127" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E127" s="3">
-        <v>26486</v>
-      </c>
+      <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128">
@@ -2934,9 +2790,7 @@
       <c r="D129" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E129" s="3">
-        <v>54396</v>
-      </c>
+      <c r="E129" s="3"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130">
@@ -2951,9 +2805,7 @@
       <c r="D130" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E130" s="3">
-        <v>27143</v>
-      </c>
+      <c r="E130" s="3"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131">
@@ -2968,9 +2820,7 @@
       <c r="D131" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E131" s="3">
-        <v>26548</v>
-      </c>
+      <c r="E131" s="3"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132">
@@ -2985,9 +2835,7 @@
       <c r="D132" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E132" s="3">
-        <v>32388</v>
-      </c>
+      <c r="E132" s="3"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133">
@@ -3002,9 +2850,7 @@
       <c r="D133" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E133" s="3">
-        <v>26116</v>
-      </c>
+      <c r="E133" s="3"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134">
@@ -3019,9 +2865,7 @@
       <c r="D134" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E134" s="3">
-        <v>56452</v>
-      </c>
+      <c r="E134" s="3"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135">
@@ -3085,9 +2929,7 @@
       <c r="D138" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E138" s="3">
-        <v>41554</v>
-      </c>
+      <c r="E138" s="3"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139">
@@ -3102,9 +2944,7 @@
       <c r="D139" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E139" s="3">
-        <v>34566</v>
-      </c>
+      <c r="E139" s="3"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140">
@@ -3119,9 +2959,7 @@
       <c r="D140" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E140" s="3">
-        <v>31061</v>
-      </c>
+      <c r="E140" s="3"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141">
@@ -3136,9 +2974,7 @@
       <c r="D141" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E141" s="3">
-        <v>24501</v>
-      </c>
+      <c r="E141" s="3"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142">
@@ -3153,9 +2989,7 @@
       <c r="D142" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E142" s="3">
-        <v>22905</v>
-      </c>
+      <c r="E142" s="3"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143">
@@ -3170,9 +3004,7 @@
       <c r="D143" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E143" s="3">
-        <v>45163</v>
-      </c>
+      <c r="E143" s="3"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144">
@@ -3187,9 +3019,7 @@
       <c r="D144" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E144" s="3">
-        <v>44881</v>
-      </c>
+      <c r="E144" s="3"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145">
@@ -3204,9 +3034,7 @@
       <c r="D145" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E145" s="3">
-        <v>56804</v>
-      </c>
+      <c r="E145" s="3"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146">
@@ -3238,9 +3066,7 @@
       <c r="D147" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E147" s="3">
-        <v>18640</v>
-      </c>
+      <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148">
@@ -3272,9 +3098,7 @@
       <c r="D149" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E149" s="3">
-        <v>31865</v>
-      </c>
+      <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150">
@@ -3306,9 +3130,7 @@
       <c r="D151" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E151" s="3">
-        <v>33337</v>
-      </c>
+      <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152">
@@ -3340,9 +3162,7 @@
       <c r="D153" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E153" s="3">
-        <v>39650</v>
-      </c>
+      <c r="E153" s="3"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154">
@@ -3391,9 +3211,7 @@
       <c r="D156" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E156" s="3">
-        <v>36411</v>
-      </c>
+      <c r="E156" s="3"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157">
@@ -3459,9 +3277,7 @@
       <c r="D160" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E160" s="3">
-        <v>37202</v>
-      </c>
+      <c r="E160" s="3"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161">
@@ -3510,9 +3326,7 @@
       <c r="D163" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E163" s="3">
-        <v>30020</v>
-      </c>
+      <c r="E163" s="3"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164">
@@ -3559,9 +3373,7 @@
       <c r="D166" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E166" s="3">
-        <v>31574</v>
-      </c>
+      <c r="E166" s="3"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167">
@@ -3576,9 +3388,7 @@
       <c r="D167" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E167" s="3">
-        <v>24964</v>
-      </c>
+      <c r="E167" s="3"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168">
@@ -3610,9 +3420,7 @@
       <c r="D169" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E169" s="3">
-        <v>33188</v>
-      </c>
+      <c r="E169" s="3"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170">
@@ -3627,9 +3435,7 @@
       <c r="D170" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E170" s="3">
-        <v>30720</v>
-      </c>
+      <c r="E170" s="3"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171">
@@ -3644,9 +3450,7 @@
       <c r="D171" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E171" s="3">
-        <v>32109</v>
-      </c>
+      <c r="E171" s="3"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172">
@@ -3661,9 +3465,7 @@
       <c r="D172" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E172" s="3">
-        <v>27074</v>
-      </c>
+      <c r="E172" s="3"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173">
@@ -3678,9 +3480,7 @@
       <c r="D173" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E173" s="3">
-        <v>24964</v>
-      </c>
+      <c r="E173" s="3"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174">
@@ -3695,9 +3495,7 @@
       <c r="D174" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E174" s="3">
-        <v>21764</v>
-      </c>
+      <c r="E174" s="3"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175">
@@ -3712,9 +3510,7 @@
       <c r="D175" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E175" s="3">
-        <v>22703</v>
-      </c>
+      <c r="E175" s="3"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176">
@@ -3758,7 +3554,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2295F436-F459-4592-B1A8-8A62A977B3B3}">
-  <dimension ref="A1:K177"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
@@ -3772,9 +3568,11 @@
     <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.8984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="73.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3808,8 +3606,14 @@
       <c r="K1" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>5917921</v>
       </c>
@@ -3840,8 +3644,14 @@
       <c r="J2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M2" s="3">
+        <v>108280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>6880719</v>
       </c>
@@ -3869,8 +3679,14 @@
       <c r="J3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M3" s="3">
+        <v>148972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1276220</v>
       </c>
@@ -3904,8 +3720,14 @@
       <c r="K4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M4" s="3">
+        <v>61904</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>6997603</v>
       </c>
@@ -3933,8 +3755,14 @@
       <c r="J5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L5" t="s">
+        <v>115</v>
+      </c>
+      <c r="M5" s="3">
+        <v>74892</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>6962674</v>
       </c>
@@ -3965,8 +3793,14 @@
       <c r="J6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M6" s="3">
+        <v>45281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6998388</v>
       </c>
@@ -3994,8 +3828,14 @@
       <c r="J7" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M7" s="3">
+        <v>108842</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>3778985</v>
       </c>
@@ -4023,8 +3863,17 @@
       <c r="J8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M8" s="3">
+        <v>64664</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>3289926</v>
       </c>
@@ -4052,8 +3901,14 @@
       <c r="J9" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L9" t="s">
+        <v>114</v>
+      </c>
+      <c r="M9" s="3">
+        <v>45368</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>1712288</v>
       </c>
@@ -4081,8 +3936,14 @@
       <c r="J10" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L10" t="s">
+        <v>115</v>
+      </c>
+      <c r="M10" s="3">
+        <v>49076</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>6759952</v>
       </c>
@@ -4110,8 +3971,14 @@
       <c r="J11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L11" t="s">
+        <v>115</v>
+      </c>
+      <c r="M11" s="3">
+        <v>41556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2508604</v>
       </c>
@@ -4139,8 +4006,14 @@
       <c r="J12" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L12" t="s">
+        <v>114</v>
+      </c>
+      <c r="M12" s="3">
+        <v>47094</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>5889691</v>
       </c>
@@ -4168,8 +4041,14 @@
       <c r="J13" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L13" t="s">
+        <v>115</v>
+      </c>
+      <c r="M13" s="3">
+        <v>43214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>5370212</v>
       </c>
@@ -4197,8 +4076,17 @@
       <c r="J14" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" t="s">
+        <v>115</v>
+      </c>
+      <c r="M14" s="3">
+        <v>68095</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>5855587</v>
       </c>
@@ -4226,8 +4114,14 @@
       <c r="J15" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L15" t="s">
+        <v>115</v>
+      </c>
+      <c r="M15" s="3">
+        <v>42185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2010988</v>
       </c>
@@ -4255,8 +4149,14 @@
       <c r="J16" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L16" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="3">
+        <v>39355</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>6999784</v>
       </c>
@@ -4284,8 +4184,14 @@
       <c r="J17" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L17" t="s">
+        <v>115</v>
+      </c>
+      <c r="M17" s="3">
+        <v>41864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1211072</v>
       </c>
@@ -4313,8 +4219,14 @@
       <c r="J18" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L18" t="s">
+        <v>115</v>
+      </c>
+      <c r="M18" s="3">
+        <v>44815</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>3502564</v>
       </c>
@@ -4342,8 +4254,14 @@
       <c r="J19" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L19" t="s">
+        <v>115</v>
+      </c>
+      <c r="M19" s="3">
+        <v>29564</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>4008721</v>
       </c>
@@ -4371,8 +4289,14 @@
       <c r="K20" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L20" t="s">
+        <v>114</v>
+      </c>
+      <c r="M20" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>6362343</v>
       </c>
@@ -4400,8 +4324,14 @@
       <c r="J21" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M21" s="3">
+        <v>65213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>3315694</v>
       </c>
@@ -4432,8 +4362,14 @@
       <c r="J22" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L22" t="s">
+        <v>115</v>
+      </c>
+      <c r="M22" s="3">
+        <v>46488</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>3870955</v>
       </c>
@@ -4461,8 +4397,14 @@
       <c r="J23" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L23" t="s">
+        <v>115</v>
+      </c>
+      <c r="M23" s="3">
+        <v>32352</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>5971797</v>
       </c>
@@ -4490,8 +4432,14 @@
       <c r="J24" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L24" t="s">
+        <v>115</v>
+      </c>
+      <c r="M24" s="3">
+        <v>95576</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>6935475</v>
       </c>
@@ -4519,8 +4467,14 @@
       <c r="J25" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L25" t="s">
+        <v>114</v>
+      </c>
+      <c r="M25" s="3">
+        <v>29339</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>185822</v>
       </c>
@@ -4548,8 +4502,14 @@
       <c r="J26" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L26" t="s">
+        <v>114</v>
+      </c>
+      <c r="M26" s="3">
+        <v>66334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>2488131</v>
       </c>
@@ -4580,8 +4540,14 @@
       <c r="J27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L27" t="s">
+        <v>115</v>
+      </c>
+      <c r="M27" s="3">
+        <v>62218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>6138057</v>
       </c>
@@ -4609,8 +4575,14 @@
       <c r="J28" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L28" t="s">
+        <v>115</v>
+      </c>
+      <c r="M28" s="3">
+        <v>32788</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>6930918</v>
       </c>
@@ -4641,8 +4613,14 @@
       <c r="J29" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L29" t="s">
+        <v>115</v>
+      </c>
+      <c r="M29" s="3">
+        <v>22544</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1660148</v>
       </c>
@@ -4670,8 +4648,14 @@
       <c r="J30" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L30" t="s">
+        <v>115</v>
+      </c>
+      <c r="M30" s="3">
+        <v>82512</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2489715</v>
       </c>
@@ -4699,8 +4683,14 @@
       <c r="J31" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L31" t="s">
+        <v>115</v>
+      </c>
+      <c r="M31" s="3">
+        <v>26486</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>4484503</v>
       </c>
@@ -4728,8 +4718,14 @@
       <c r="J32" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L32" t="s">
+        <v>115</v>
+      </c>
+      <c r="M32" s="3">
+        <v>24768</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>4224945</v>
       </c>
@@ -4757,8 +4753,14 @@
       <c r="J33" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L33" t="s">
+        <v>115</v>
+      </c>
+      <c r="M33" s="3">
+        <v>33464</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>4427907</v>
       </c>
@@ -4786,8 +4788,14 @@
       <c r="J34" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L34" t="s">
+        <v>115</v>
+      </c>
+      <c r="M34" s="3">
+        <v>47042</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>4949523</v>
       </c>
@@ -4818,8 +4826,17 @@
       <c r="J35" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K35" t="s">
+        <v>116</v>
+      </c>
+      <c r="L35" t="s">
+        <v>115</v>
+      </c>
+      <c r="M35" s="3">
+        <v>64427</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>6946430</v>
       </c>
@@ -4847,8 +4864,14 @@
       <c r="J36" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L36" t="s">
+        <v>115</v>
+      </c>
+      <c r="M36" s="3">
+        <v>18042</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>3616123</v>
       </c>
@@ -4882,8 +4905,14 @@
       <c r="K37" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L37" t="s">
+        <v>114</v>
+      </c>
+      <c r="M37" s="3">
+        <v>28578</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>6921971</v>
       </c>
@@ -4911,8 +4940,14 @@
       <c r="J38" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L38" t="s">
+        <v>115</v>
+      </c>
+      <c r="M38" s="3">
+        <v>29564</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>917128</v>
       </c>
@@ -4946,8 +4981,14 @@
       <c r="K39" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L39" t="s">
+        <v>114</v>
+      </c>
+      <c r="M39" s="3">
+        <v>56647</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>3734971</v>
       </c>
@@ -4978,8 +5019,14 @@
       <c r="J40" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L40" t="s">
+        <v>115</v>
+      </c>
+      <c r="M40" s="3">
+        <v>35502</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>3131543</v>
       </c>
@@ -5007,8 +5054,14 @@
       <c r="J41" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L41" t="s">
+        <v>115</v>
+      </c>
+      <c r="M41" s="3">
+        <v>61984</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>5565188</v>
       </c>
@@ -5036,8 +5089,14 @@
       <c r="J42" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L42" t="s">
+        <v>114</v>
+      </c>
+      <c r="M42" s="3">
+        <v>21764</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>3197022</v>
       </c>
@@ -5065,8 +5124,14 @@
       <c r="J43" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L43" t="s">
+        <v>115</v>
+      </c>
+      <c r="M43" s="3">
+        <v>54812</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>5433913</v>
       </c>
@@ -5094,8 +5159,14 @@
       <c r="J44" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L44" t="s">
+        <v>115</v>
+      </c>
+      <c r="M44" s="3">
+        <v>50711</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>7002912</v>
       </c>
@@ -5123,8 +5194,14 @@
       <c r="J45" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L45" t="s">
+        <v>115</v>
+      </c>
+      <c r="M45" s="3">
+        <v>44154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>5047065</v>
       </c>
@@ -5152,8 +5229,14 @@
       <c r="J46" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L46" t="s">
+        <v>115</v>
+      </c>
+      <c r="M46" s="3">
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>692435</v>
       </c>
@@ -5181,8 +5264,14 @@
       <c r="J47" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L47" t="s">
+        <v>114</v>
+      </c>
+      <c r="M47" s="3">
+        <v>38927</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>4919405</v>
       </c>
@@ -5210,8 +5299,14 @@
       <c r="J48" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L48" t="s">
+        <v>115</v>
+      </c>
+      <c r="M48" s="3">
+        <v>45163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>7003229</v>
       </c>
@@ -5239,8 +5334,14 @@
       <c r="J49" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L49" t="s">
+        <v>115</v>
+      </c>
+      <c r="M49" s="3">
+        <v>37430</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>978328</v>
       </c>
@@ -5268,8 +5369,14 @@
       <c r="J50" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>115</v>
+      </c>
+      <c r="M50" s="3">
+        <v>62016</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1754844</v>
       </c>
@@ -5297,8 +5404,14 @@
       <c r="J51" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L51" t="s">
+        <v>115</v>
+      </c>
+      <c r="M51" s="3">
+        <v>39650</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>2467909</v>
       </c>
@@ -5326,8 +5439,14 @@
       <c r="J52" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L52" t="s">
+        <v>115</v>
+      </c>
+      <c r="M52" s="3">
+        <v>48036</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>2727963</v>
       </c>
@@ -5361,8 +5480,14 @@
       <c r="K53" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L53" t="s">
+        <v>114</v>
+      </c>
+      <c r="M53" s="3">
+        <v>56159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>3306936</v>
       </c>
@@ -5390,8 +5515,14 @@
       <c r="J54" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L54" t="s">
+        <v>115</v>
+      </c>
+      <c r="M54" s="3">
+        <v>35296</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>4274661</v>
       </c>
@@ -5425,8 +5556,14 @@
       <c r="K55" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>114</v>
+      </c>
+      <c r="M55" s="3">
+        <v>25664</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1696953</v>
       </c>
@@ -5454,8 +5591,14 @@
       <c r="J56" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L56" t="s">
+        <v>114</v>
+      </c>
+      <c r="M56" s="3">
+        <v>53358</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>5218587</v>
       </c>
@@ -5477,8 +5620,12 @@
       <c r="J57" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L57" t="s">
+        <v>117</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>6880151</v>
       </c>
@@ -5506,8 +5653,14 @@
       <c r="J58" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L58" t="s">
+        <v>115</v>
+      </c>
+      <c r="M58" s="3">
+        <v>21728</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>3024546</v>
       </c>
@@ -5535,8 +5688,14 @@
       <c r="J59" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L59" t="s">
+        <v>115</v>
+      </c>
+      <c r="M59" s="3">
+        <v>26811</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>6732514</v>
       </c>
@@ -5564,8 +5723,14 @@
       <c r="J60" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L60" t="s">
+        <v>115</v>
+      </c>
+      <c r="M60" s="3">
+        <v>38349</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>5636254</v>
       </c>
@@ -5590,8 +5755,12 @@
       <c r="J61" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L61" t="s">
+        <v>117</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>6799615</v>
       </c>
@@ -5619,8 +5788,14 @@
       <c r="J62" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L62" t="s">
+        <v>114</v>
+      </c>
+      <c r="M62" s="3">
+        <v>27614</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>6960339</v>
       </c>
@@ -5648,8 +5823,14 @@
       <c r="J63" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L63" t="s">
+        <v>115</v>
+      </c>
+      <c r="M63" s="3">
+        <v>58100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>2862933</v>
       </c>
@@ -5677,8 +5858,14 @@
       <c r="J64" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L64" t="s">
+        <v>114</v>
+      </c>
+      <c r="M64" s="3">
+        <v>39650</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>5269180</v>
       </c>
@@ -5706,8 +5893,14 @@
       <c r="J65" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L65" t="s">
+        <v>115</v>
+      </c>
+      <c r="M65" s="3">
+        <v>54198</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>7001768</v>
       </c>
@@ -5729,8 +5922,12 @@
       <c r="J66" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L66" t="s">
+        <v>117</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>4605361</v>
       </c>
@@ -5758,8 +5955,14 @@
       <c r="J67" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L67" t="s">
+        <v>114</v>
+      </c>
+      <c r="M67" s="3">
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>6020046</v>
       </c>
@@ -5787,8 +5990,14 @@
       <c r="J68" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L68" t="s">
+        <v>115</v>
+      </c>
+      <c r="M68" s="3">
+        <v>42432</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>6314809</v>
       </c>
@@ -5813,8 +6022,12 @@
       <c r="J69" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L69" t="s">
+        <v>117</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>6565420</v>
       </c>
@@ -5845,8 +6058,14 @@
       <c r="J70" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L70" t="s">
+        <v>115</v>
+      </c>
+      <c r="M70" s="3">
+        <v>47898</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>7005855</v>
       </c>
@@ -5874,8 +6093,14 @@
       <c r="J71" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L71" t="s">
+        <v>114</v>
+      </c>
+      <c r="M71" s="3">
+        <v>33464</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>4619601</v>
       </c>
@@ -5903,8 +6128,14 @@
       <c r="J72" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L72" t="s">
+        <v>115</v>
+      </c>
+      <c r="M72" s="3">
+        <v>47128</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>5427275</v>
       </c>
@@ -5932,8 +6163,14 @@
       <c r="J73" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L73" t="s">
+        <v>114</v>
+      </c>
+      <c r="M73" s="3">
+        <v>48131</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>3800845</v>
       </c>
@@ -5961,8 +6198,14 @@
       <c r="J74" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L74" t="s">
+        <v>114</v>
+      </c>
+      <c r="M74" s="3">
+        <v>28578</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1436977</v>
       </c>
@@ -5993,8 +6236,14 @@
       <c r="J75" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L75" t="s">
+        <v>114</v>
+      </c>
+      <c r="M75" s="3">
+        <v>19026</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>2146062</v>
       </c>
@@ -6022,8 +6271,14 @@
       <c r="J76" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L76" t="s">
+        <v>115</v>
+      </c>
+      <c r="M76" s="3">
+        <v>27614</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>2915405</v>
       </c>
@@ -6054,8 +6309,14 @@
       <c r="J77" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L77" t="s">
+        <v>114</v>
+      </c>
+      <c r="M77" s="3">
+        <v>42750</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>2984892</v>
       </c>
@@ -6083,8 +6344,14 @@
       <c r="J78" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L78" t="s">
+        <v>115</v>
+      </c>
+      <c r="M78" s="3">
+        <v>51210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>4244478</v>
       </c>
@@ -6112,8 +6379,14 @@
       <c r="J79" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L79" t="s">
+        <v>115</v>
+      </c>
+      <c r="M79" s="3">
+        <v>53011</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>4583363</v>
       </c>
@@ -6141,8 +6414,14 @@
       <c r="J80" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L80" t="s">
+        <v>115</v>
+      </c>
+      <c r="M80" s="3">
+        <v>56003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>6031532</v>
       </c>
@@ -6170,8 +6449,14 @@
       <c r="J81" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L81" t="s">
+        <v>114</v>
+      </c>
+      <c r="M81" s="3">
+        <v>49180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>6705226</v>
       </c>
@@ -6202,8 +6487,14 @@
       <c r="J82" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L82" t="s">
+        <v>115</v>
+      </c>
+      <c r="M82" s="3">
+        <v>18840</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>6783496</v>
       </c>
@@ -6228,8 +6519,12 @@
       <c r="J83" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L83" t="s">
+        <v>117</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>6823288</v>
       </c>
@@ -6257,8 +6552,14 @@
       <c r="J84" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L84" t="s">
+        <v>115</v>
+      </c>
+      <c r="M84" s="3">
+        <v>45368</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>6841363</v>
       </c>
@@ -6286,8 +6587,14 @@
       <c r="J85" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L85" t="s">
+        <v>115</v>
+      </c>
+      <c r="M85" s="3">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>7006972</v>
       </c>
@@ -6312,8 +6619,12 @@
       <c r="J86" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L86" t="s">
+        <v>117</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>7007241</v>
       </c>
@@ -6341,8 +6652,14 @@
       <c r="J87" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L87" t="s">
+        <v>115</v>
+      </c>
+      <c r="M87" s="3">
+        <v>47042</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>224181</v>
       </c>
@@ -6370,8 +6687,14 @@
       <c r="J88" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L88" t="s">
+        <v>115</v>
+      </c>
+      <c r="M88" s="3">
+        <v>14867</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>3046984</v>
       </c>
@@ -6399,8 +6722,14 @@
       <c r="J89" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L89" t="s">
+        <v>114</v>
+      </c>
+      <c r="M89" s="3">
+        <v>66149</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>4348909</v>
       </c>
@@ -6428,8 +6757,14 @@
       <c r="J90" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L90" t="s">
+        <v>114</v>
+      </c>
+      <c r="M90" s="3">
+        <v>16140</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>7007645</v>
       </c>
@@ -6457,8 +6792,14 @@
       <c r="J91" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L91" t="s">
+        <v>115</v>
+      </c>
+      <c r="M91" s="3">
+        <v>26811</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>2420963</v>
       </c>
@@ -6489,8 +6830,14 @@
       <c r="J92" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L92" t="s">
+        <v>114</v>
+      </c>
+      <c r="M92" s="3">
+        <v>29363</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>2581999</v>
       </c>
@@ -6518,8 +6865,14 @@
       <c r="J93" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L93" t="s">
+        <v>115</v>
+      </c>
+      <c r="M93" s="3">
+        <v>13302</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>5621102</v>
       </c>
@@ -6547,8 +6900,14 @@
       <c r="J94" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L94" t="s">
+        <v>115</v>
+      </c>
+      <c r="M94" s="3">
+        <v>28658</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>7002013</v>
       </c>
@@ -6579,8 +6938,14 @@
       <c r="K95" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L95" t="s">
+        <v>114</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>7007760</v>
       </c>
@@ -6608,8 +6973,14 @@
       <c r="J96" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L96" t="s">
+        <v>115</v>
+      </c>
+      <c r="M96" s="3">
+        <v>60854</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>3578323</v>
       </c>
@@ -6640,8 +7011,14 @@
       <c r="J97" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L97" t="s">
+        <v>115</v>
+      </c>
+      <c r="M97" s="3">
+        <v>39039</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>6716596</v>
       </c>
@@ -6669,8 +7046,14 @@
       <c r="J98" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L98" t="s">
+        <v>114</v>
+      </c>
+      <c r="M98" s="3">
+        <v>48997</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>6980367</v>
       </c>
@@ -6698,8 +7081,14 @@
       <c r="J99" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L99" t="s">
+        <v>115</v>
+      </c>
+      <c r="M99" s="3">
+        <v>64333</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>3525233</v>
       </c>
@@ -6727,8 +7116,14 @@
       <c r="J100" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L100" t="s">
+        <v>115</v>
+      </c>
+      <c r="M100" s="3">
+        <v>34566</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>5952812</v>
       </c>
@@ -6756,8 +7151,14 @@
       <c r="J101" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L101" t="s">
+        <v>115</v>
+      </c>
+      <c r="M101" s="3">
+        <v>38742</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>6644947</v>
       </c>
@@ -6785,8 +7186,14 @@
       <c r="J102" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L102" t="s">
+        <v>115</v>
+      </c>
+      <c r="M102" s="3">
+        <v>45368</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>5404924</v>
       </c>
@@ -6817,8 +7224,14 @@
       <c r="J103" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L103" t="s">
+        <v>115</v>
+      </c>
+      <c r="M103" s="3">
+        <v>43065</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>6935475</v>
       </c>
@@ -6846,8 +7259,14 @@
       <c r="J104" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L104" t="s">
+        <v>115</v>
+      </c>
+      <c r="M104" s="3">
+        <v>29564</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>5881986</v>
       </c>
@@ -6878,8 +7297,14 @@
       <c r="J105" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L105" t="s">
+        <v>114</v>
+      </c>
+      <c r="M105" s="3">
+        <v>25120</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>6563589</v>
       </c>
@@ -6910,8 +7335,14 @@
       <c r="J106" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L106" t="s">
+        <v>115</v>
+      </c>
+      <c r="M106" s="3">
+        <v>43679</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>1638228</v>
       </c>
@@ -6942,8 +7373,14 @@
       <c r="J107" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L107" t="s">
+        <v>115</v>
+      </c>
+      <c r="M107" s="3">
+        <v>27529</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>5967130</v>
       </c>
@@ -6971,8 +7408,14 @@
       <c r="J108" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L108" t="s">
+        <v>114</v>
+      </c>
+      <c r="M108" s="3">
+        <v>85956</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>4015942</v>
       </c>
@@ -7000,8 +7443,14 @@
       <c r="J109" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L109" t="s">
+        <v>115</v>
+      </c>
+      <c r="M109" s="3">
+        <v>30020</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>450255</v>
       </c>
@@ -7029,8 +7478,14 @@
       <c r="J110" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L110" t="s">
+        <v>115</v>
+      </c>
+      <c r="M110" s="3">
+        <v>77770</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>3289279</v>
       </c>
@@ -7058,8 +7513,14 @@
       <c r="J111" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L111" t="s">
+        <v>115</v>
+      </c>
+      <c r="M111" s="3">
+        <v>49257</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>6983084</v>
       </c>
@@ -7087,8 +7548,14 @@
       <c r="J112" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L112" t="s">
+        <v>115</v>
+      </c>
+      <c r="M112" s="3">
+        <v>62416</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>1842372</v>
       </c>
@@ -7116,8 +7583,14 @@
       <c r="J113" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L113" t="s">
+        <v>115</v>
+      </c>
+      <c r="M113" s="3">
+        <v>38742</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>4148967</v>
       </c>
@@ -7145,8 +7618,14 @@
       <c r="J114" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L114" t="s">
+        <v>114</v>
+      </c>
+      <c r="M114" s="3">
+        <v>26486</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>6341313</v>
       </c>
@@ -7171,8 +7650,12 @@
       <c r="J115" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L115" t="s">
+        <v>117</v>
+      </c>
+      <c r="M115" s="3"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>5717371</v>
       </c>
@@ -7200,8 +7683,14 @@
       <c r="J116" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L116" t="s">
+        <v>115</v>
+      </c>
+      <c r="M116" s="3">
+        <v>18042</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>7010022</v>
       </c>
@@ -7232,8 +7721,14 @@
       <c r="J117" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L117" t="s">
+        <v>115</v>
+      </c>
+      <c r="M117" s="3">
+        <v>33803</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>507535</v>
       </c>
@@ -7261,8 +7756,14 @@
       <c r="J118" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L118" t="s">
+        <v>115</v>
+      </c>
+      <c r="M118" s="3">
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>2638813</v>
       </c>
@@ -7290,8 +7791,14 @@
       <c r="J119" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L119" t="s">
+        <v>115</v>
+      </c>
+      <c r="M119" s="3">
+        <v>45121</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>4224945</v>
       </c>
@@ -7313,8 +7820,12 @@
       <c r="J120" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L120" t="s">
+        <v>117</v>
+      </c>
+      <c r="M120" s="3"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>4192390</v>
       </c>
@@ -7342,8 +7853,14 @@
       <c r="J121" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L121" t="s">
+        <v>115</v>
+      </c>
+      <c r="M121" s="3">
+        <v>51014</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>5186336</v>
       </c>
@@ -7371,8 +7888,14 @@
       <c r="J122" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L122" t="s">
+        <v>115</v>
+      </c>
+      <c r="M122" s="3">
+        <v>20284</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>5658298</v>
       </c>
@@ -7400,8 +7923,14 @@
       <c r="J123" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L123" t="s">
+        <v>115</v>
+      </c>
+      <c r="M123" s="3">
+        <v>17479</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>6961622</v>
       </c>
@@ -7429,8 +7958,14 @@
       <c r="J124" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L124" t="s">
+        <v>114</v>
+      </c>
+      <c r="M124" s="3">
+        <v>29363</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>6964692</v>
       </c>
@@ -7464,8 +7999,14 @@
       <c r="K125" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L125" t="s">
+        <v>114</v>
+      </c>
+      <c r="M125" s="3">
+        <v>27372</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>7008445</v>
       </c>
@@ -7493,8 +8034,14 @@
       <c r="J126" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L126" t="s">
+        <v>114</v>
+      </c>
+      <c r="M126" s="3">
+        <v>27143</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>2026121</v>
       </c>
@@ -7522,8 +8069,14 @@
       <c r="J127" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L127" t="s">
+        <v>115</v>
+      </c>
+      <c r="M127" s="3">
+        <v>26486</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>4002781</v>
       </c>
@@ -7554,8 +8107,14 @@
       <c r="K128" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L128" t="s">
+        <v>114</v>
+      </c>
+      <c r="M128" s="3">
+        <v>46536</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>6903872</v>
       </c>
@@ -7583,8 +8142,14 @@
       <c r="J129" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L129" t="s">
+        <v>115</v>
+      </c>
+      <c r="M129" s="3">
+        <v>54396</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>1828865</v>
       </c>
@@ -7615,8 +8180,14 @@
       <c r="J130" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L130" t="s">
+        <v>115</v>
+      </c>
+      <c r="M130" s="3">
+        <v>27143</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>4408589</v>
       </c>
@@ -7647,8 +8218,14 @@
       <c r="J131" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L131" t="s">
+        <v>115</v>
+      </c>
+      <c r="M131" s="3">
+        <v>26548</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>4724414</v>
       </c>
@@ -7676,8 +8253,14 @@
       <c r="J132" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L132" t="s">
+        <v>115</v>
+      </c>
+      <c r="M132" s="3">
+        <v>32388</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>7011062</v>
       </c>
@@ -7708,8 +8291,14 @@
       <c r="J133" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L133" t="s">
+        <v>115</v>
+      </c>
+      <c r="M133" s="3">
+        <v>26116</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>7011214</v>
       </c>
@@ -7737,8 +8326,14 @@
       <c r="J134" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L134" t="s">
+        <v>115</v>
+      </c>
+      <c r="M134" s="3">
+        <v>56452</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>7011341</v>
       </c>
@@ -7769,8 +8364,14 @@
       <c r="J135" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L135" t="s">
+        <v>114</v>
+      </c>
+      <c r="M135" s="3">
+        <v>59447</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>5072765</v>
       </c>
@@ -7798,8 +8399,14 @@
       <c r="J136" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L136" t="s">
+        <v>114</v>
+      </c>
+      <c r="M136" s="3">
+        <v>52764</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>4168488</v>
       </c>
@@ -7827,8 +8434,14 @@
       <c r="K137" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L137" t="s">
+        <v>115</v>
+      </c>
+      <c r="M137" s="3">
+        <v>45164</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>6027963</v>
       </c>
@@ -7856,8 +8469,14 @@
       <c r="J138" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L138" t="s">
+        <v>115</v>
+      </c>
+      <c r="M138" s="3">
+        <v>41554</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>7011745</v>
       </c>
@@ -7885,8 +8504,14 @@
       <c r="J139" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L139" t="s">
+        <v>115</v>
+      </c>
+      <c r="M139" s="3">
+        <v>34566</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>7011769</v>
       </c>
@@ -7917,8 +8542,14 @@
       <c r="J140" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L140" t="s">
+        <v>115</v>
+      </c>
+      <c r="M140" s="3">
+        <v>31061</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>4779015</v>
       </c>
@@ -7946,8 +8577,14 @@
       <c r="J141" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L141" t="s">
+        <v>115</v>
+      </c>
+      <c r="M141" s="3">
+        <v>24501</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>5490711</v>
       </c>
@@ -7975,8 +8612,14 @@
       <c r="J142" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L142" t="s">
+        <v>115</v>
+      </c>
+      <c r="M142" s="3">
+        <v>22905</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>6178114</v>
       </c>
@@ -8007,8 +8650,14 @@
       <c r="J143" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L143" t="s">
+        <v>115</v>
+      </c>
+      <c r="M143" s="3">
+        <v>45163</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>6531075</v>
       </c>
@@ -8036,8 +8685,14 @@
       <c r="J144" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L144" t="s">
+        <v>115</v>
+      </c>
+      <c r="M144" s="3">
+        <v>44881</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>6783321</v>
       </c>
@@ -8065,8 +8720,14 @@
       <c r="J145" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L145" t="s">
+        <v>115</v>
+      </c>
+      <c r="M145" s="3">
+        <v>56804</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>5074517</v>
       </c>
@@ -8094,8 +8755,14 @@
       <c r="J146" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L146" t="s">
+        <v>114</v>
+      </c>
+      <c r="M146" s="3">
+        <v>40776</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>7002291</v>
       </c>
@@ -8123,8 +8790,14 @@
       <c r="J147" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L147" t="s">
+        <v>115</v>
+      </c>
+      <c r="M147" s="3">
+        <v>18640</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>7012242</v>
       </c>
@@ -8155,8 +8828,14 @@
       <c r="J148" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L148" t="s">
+        <v>114</v>
+      </c>
+      <c r="M148" s="3">
+        <v>35826</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>7012278</v>
       </c>
@@ -8184,8 +8863,14 @@
       <c r="J149" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L149" t="s">
+        <v>115</v>
+      </c>
+      <c r="M149" s="3">
+        <v>31865</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>4824290</v>
       </c>
@@ -8213,8 +8898,14 @@
       <c r="J150" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L150" t="s">
+        <v>114</v>
+      </c>
+      <c r="M150" s="3">
+        <v>32109</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>6867292</v>
       </c>
@@ -8245,8 +8936,14 @@
       <c r="J151" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L151" t="s">
+        <v>115</v>
+      </c>
+      <c r="M151" s="3">
+        <v>33337</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>6995926</v>
       </c>
@@ -8274,8 +8971,14 @@
       <c r="J152" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L152" t="s">
+        <v>114</v>
+      </c>
+      <c r="M152" s="3">
+        <v>26673</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>5234935</v>
       </c>
@@ -8303,8 +9006,14 @@
       <c r="J153" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L153" t="s">
+        <v>115</v>
+      </c>
+      <c r="M153" s="3">
+        <v>39650</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>7002342</v>
       </c>
@@ -8332,8 +9041,14 @@
       <c r="J154" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L154" t="s">
+        <v>114</v>
+      </c>
+      <c r="M154" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>5940780</v>
       </c>
@@ -8367,8 +9082,14 @@
       <c r="K155" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L155" t="s">
+        <v>114</v>
+      </c>
+      <c r="M155" s="3">
+        <v>47094</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>6088581</v>
       </c>
@@ -8396,8 +9117,14 @@
       <c r="J156" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L156" t="s">
+        <v>115</v>
+      </c>
+      <c r="M156" s="3">
+        <v>36411</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>4025880</v>
       </c>
@@ -8431,8 +9158,14 @@
       <c r="K157" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L157" t="s">
+        <v>114</v>
+      </c>
+      <c r="M157" s="3">
+        <v>47123</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>6523319</v>
       </c>
@@ -8460,8 +9193,14 @@
       <c r="J158" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L158" t="s">
+        <v>114</v>
+      </c>
+      <c r="M158" s="3">
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>5815634</v>
       </c>
@@ -8489,8 +9228,14 @@
       <c r="J159" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L159" t="s">
+        <v>114</v>
+      </c>
+      <c r="M159" s="3">
+        <v>44103</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>6909329</v>
       </c>
@@ -8518,8 +9263,14 @@
       <c r="J160" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L160" t="s">
+        <v>115</v>
+      </c>
+      <c r="M160" s="3">
+        <v>37202</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>6999809</v>
       </c>
@@ -8547,8 +9298,14 @@
       <c r="J161" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L161" t="s">
+        <v>114</v>
+      </c>
+      <c r="M161" s="3">
+        <v>39775</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>7013787</v>
       </c>
@@ -8576,8 +9333,14 @@
       <c r="J162" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L162" t="s">
+        <v>114</v>
+      </c>
+      <c r="M162" s="3">
+        <v>38888</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>2786082</v>
       </c>
@@ -8605,8 +9368,14 @@
       <c r="J163" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L163" t="s">
+        <v>115</v>
+      </c>
+      <c r="M163" s="3">
+        <v>30020</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>6300230</v>
       </c>
@@ -8634,8 +9403,14 @@
       <c r="J164" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L164" t="s">
+        <v>114</v>
+      </c>
+      <c r="M164" s="3">
+        <v>29104</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>6725672</v>
       </c>
@@ -8660,8 +9435,12 @@
       <c r="J165" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L165" t="s">
+        <v>117</v>
+      </c>
+      <c r="M165" s="3"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>3988182</v>
       </c>
@@ -8689,8 +9468,14 @@
       <c r="J166" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L166" t="s">
+        <v>115</v>
+      </c>
+      <c r="M166" s="3">
+        <v>31574</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>4907602</v>
       </c>
@@ -8718,8 +9503,14 @@
       <c r="J167" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L167" t="s">
+        <v>115</v>
+      </c>
+      <c r="M167" s="3">
+        <v>24964</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>6693180</v>
       </c>
@@ -8747,8 +9538,14 @@
       <c r="J168" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L168" t="s">
+        <v>114</v>
+      </c>
+      <c r="M168" s="3">
+        <v>29766</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>2959572</v>
       </c>
@@ -8779,8 +9576,14 @@
       <c r="J169" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L169" t="s">
+        <v>115</v>
+      </c>
+      <c r="M169" s="3">
+        <v>33188</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>2960032</v>
       </c>
@@ -8808,8 +9611,14 @@
       <c r="J170" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L170" t="s">
+        <v>115</v>
+      </c>
+      <c r="M170" s="3">
+        <v>30720</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>2344226</v>
       </c>
@@ -8837,8 +9646,14 @@
       <c r="J171" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L171" t="s">
+        <v>115</v>
+      </c>
+      <c r="M171" s="3">
+        <v>32109</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>6064959</v>
       </c>
@@ -8866,8 +9681,14 @@
       <c r="J172" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L172" t="s">
+        <v>115</v>
+      </c>
+      <c r="M172" s="3">
+        <v>27074</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>6971510</v>
       </c>
@@ -8895,8 +9716,14 @@
       <c r="J173" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L173" t="s">
+        <v>115</v>
+      </c>
+      <c r="M173" s="3">
+        <v>24964</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>2049282</v>
       </c>
@@ -8924,8 +9751,14 @@
       <c r="J174" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L174" t="s">
+        <v>115</v>
+      </c>
+      <c r="M174" s="3">
+        <v>21764</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>5557535</v>
       </c>
@@ -8953,8 +9786,14 @@
       <c r="J175" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L175" t="s">
+        <v>115</v>
+      </c>
+      <c r="M175" s="3">
+        <v>22703</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>7014412</v>
       </c>
@@ -8988,8 +9827,14 @@
       <c r="K176" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="L176" t="s">
+        <v>114</v>
+      </c>
+      <c r="M176" s="3">
+        <v>14288</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>2305250</v>
       </c>
@@ -9016,6 +9861,12 @@
       </c>
       <c r="J177" t="s">
         <v>87</v>
+      </c>
+      <c r="L177" t="s">
+        <v>114</v>
+      </c>
+      <c r="M177" s="3">
+        <v>25926</v>
       </c>
     </row>
   </sheetData>
